--- a/output/analysis.xlsx
+++ b/output/analysis.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw_Aggregates" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Segmentation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Offer_Economics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Test_Design" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Verification_Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Problem_Principles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Raw_Aggregates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Segmentation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Offer_Economics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Test_Design" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Verification_Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,6 +436,634 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Проблема — в цифрах</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MAU без кешбэка</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>36% (1,15 млн чел.)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>дано в кейсе</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Доля выбравших, не набравших 1000₽ из 3000₽</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>дано в кейсе</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Доля выбравших "Все покупки" не глядя</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>дано в кейсе; помечено как симптом причин 1-2, не отдельная причина</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Дефицит программы сегодня — сверка двумя независимыми методами</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Метод</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Оборот базы/мес</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Доход банка (1,1%)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Расход на кешбэк (факт)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Чистый результат</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1. Bottom-up по факту выборки (100к→3,2М)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>47 703 772 470 ₽</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>524 741 497 ₽</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>670 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-145 258 503 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2. Top-down по ориентирам кейса (750₽×20 тр/мес)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>48 000 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>528 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>670 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-142 000 000 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Вывод</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Оба метода независимо сходятся на убытке ≈142-145 млн ₽/мес (расхождение 2,3%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Это в 14 раз больше порога, который команда считает допустимым (~10 млн ₽/мес) — Направление A нарушено уже сегодня, без единого изменения логики.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Пять причин (проверены против данных и кейса)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Причина</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Простыми словами</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Чем подтверждается</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Трение выбора</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Лень/жалко времени на сам акт выбора 4 из 8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>36% не открывающих селектор ~= 36% без кешбэка вообще</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Категории не совпадают с тратами</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Предложенные категории не совпадают с реальными тратами</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Пенетрация: Супермаркеты 99,3%, Розница 91,9% vs Азартные игры 0,6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Награда слишком маленькая</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Сумма такая маленькая, что не стоит усилий</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>При 5% для 1000₽ нужен оборот ≥20 000₽/мес в выбранных категориях; у 76,1% выборки оборот ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Забывчивость</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Забыл зайти и выбрать, дефолта нет</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Интервью; неизмеримо в транзакционных данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Карта не основная</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Траты идут через другой банк</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Интервью; неизмеримо в данных этого банка</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Целевая рамка</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Направление A (принято)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Расход на кешбэк не должен заметно превышать доход от транзакций; допустимое ухудшение ~10 млн ₽/мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Направление B (отклонено командой)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Кешбэк как приманка для кредиток — данных о портфеле кредитных продуктов нет, не проверяемо на имеющихся данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Целевая метрика и guardrail (детальные формулы — переносятся в Test_Design при сборке Фазы 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Метрика</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Формула / порог</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Primary KPI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Coverage rate</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Доля MAU, получающих кешбэк</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Primary KPI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Transactions per MAU</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Число транзакций на MAU в месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary KPI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Spend per MAU</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Траты на MAU в месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guardrail (приростный)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Приростный P&amp;L</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Доп. доход от прироста оборота минус доп. расход на кешбэк конкретного изменения</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guardrail (полный, обязательный)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Полный P&amp;L программы</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Доход (1,1% × весь оборот базы) минус ПОЛНЫЙ расход на кешбэк (факт + все включённые изменения); порог Направления A ~10 млн ₽/мес</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Четыре принципа (дополняют друг друга, не конкурируют)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Принцип</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Что меняется</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Для кого</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>На что влияет</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Ограничение / экономика (флэт-5%, до уточнения на сегментации)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Авто-дефолт для "молчунов"</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Автоприсвоение 4 категорий по истории трат при отсутствии выбора до 28-го</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>36% MAU (~1,15 млн)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Доля с нулевым кешбэком (36%)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Полный охват ~451 млн ₽/мес. Пилот под A (~10 млн доп.бюджета): ~25,6 тыс. чел., ~2,2% группы</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Сегментированное меню 8 категорий</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Список категорий подбирается под группу, не единый для всех</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Пользователи с нетипичной структурой трат</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Доля недобора 1000₽ (28%)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Механика/кап без изменений — структурно бесплатно, расход не растёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Явная опция "Все покупки"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Один из 8 слотов - широкий кешбэк на весь оборот, как осознанный выбор</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>~12% базы (генералисты, груб. оценка)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Релевантность для генералистов; риск "не глядя" (15%)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Полный охват ~149 млн ₽/мес. Пилот под A: ~25,7 тыс. чел., ~6,7% сегмента</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Дифференцированная ставка по категориям</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ставка ниже там, где пенетрация и так высокая (напр. Супермаркеты 99,3%); высвобожденное финансирует П.1 и П.3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Вся структура вознаграждения целиком</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Сам месячный дефицит (142-145 млн) - сокращение, не только контроль прироста</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Иллюстративно ~100-250 млн ₽/мес высвобождается - неоткалибровано, требует точного расчёта на финальной сегментации (Фаза 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Рамочное ограничение (не 5-й принцип)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>"Карта не основная" не решается настройкой кешбэка - за периметром логики программы, требует отдельного продукта/канала.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -940,7 +1569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1558,7 +2187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1757,14 +2386,9 @@
       <c r="C7" t="n">
         <v>3200000</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2106173729</v>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1772,16 +2396,9 @@
           <t>Факт (дано в кейсе)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>670000000</v>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1789,18 +2406,11 @@
           <t>Отношение верхней границы к факту</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>3.14x</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1849,7 +2459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2303,7 +2913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
